--- a/config/key_ratio_rulebook.xlsx
+++ b/config/key_ratio_rulebook.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -910,17 +910,22 @@
           <t>placeholders</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>variables</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -952,13 +957,18 @@
           <t>{metric_name},{y_prev},{v_prev},{y_curr},{v_curr},{trend_word}</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>metric_name,y_prev,v_prev,y_curr,v_curr,trend_word</t>
+        </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>总述</t>
         </is>
@@ -990,13 +1000,18 @@
           <t>{driver_1},{contrib_1},{share_1}</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>driver_1,contrib_1,share_1</t>
+        </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>20</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>单驱动</t>
         </is>
@@ -1028,13 +1043,18 @@
           <t>{driver_1},{driver_2},{contrib_1},{contrib_2},{share_sum}</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>driver_1,driver_2,contrib_1,contrib_2,share_sum</t>
+        </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>双驱动</t>
         </is>
@@ -1066,13 +1086,18 @@
           <t>{driver_list}</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>driver_list</t>
+        </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>40</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>多驱动</t>
         </is>
@@ -1104,13 +1129,18 @@
           <t>{offset_driver},{offset_contrib},{main_driver}</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>offset_driver,offset_contrib,main_driver</t>
+        </is>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>50</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>对冲</t>
         </is>
@@ -1142,13 +1172,18 @@
           <t>{primary_driver},{secondary_driver},{secondary_contrib}</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>primary_driver,secondary_driver,secondary_contrib</t>
+        </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>二级驱动衔接</t>
         </is>
@@ -1180,13 +1215,18 @@
           <t>{metric_name},{y_prev},{v_prev},{y_curr},{v_curr},{trend_word}</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>metric_name,y_prev,v_prev,y_curr,v_curr,trend_word</t>
+        </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>总述</t>
         </is>
@@ -1218,13 +1258,18 @@
           <t>{driver_1},{contrib_1},{share_1}</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>driver_1,contrib_1,share_1</t>
+        </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>20</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>单驱动</t>
         </is>
@@ -1256,13 +1301,18 @@
           <t>{driver_1},{driver_2},{contrib_1},{contrib_2},{share_sum}</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>driver_1,driver_2,contrib_1,contrib_2,share_sum</t>
+        </is>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>30</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>双驱动</t>
         </is>
@@ -1294,13 +1344,18 @@
           <t>{structure_effect},{price_cost_effect},{interaction_effect}</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>structure_effect,price_cost_effect,interaction_effect</t>
+        </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>40</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>效应分解</t>
         </is>
@@ -1332,13 +1387,18 @@
           <t>{impact_summary}</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>impact_summary</t>
+        </is>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>50</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>特殊情形</t>
         </is>
@@ -1370,13 +1430,18 @@
           <t>{driver_list}</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>driver_list</t>
+        </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>35</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
@@ -1408,13 +1473,18 @@
           <t>{y1},{y2},{y3},{nm1},{nm2},{nm3},{at1},{at2},{at3},{em1},{em2},{em3}</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>y1,nm1,y2,nm2,y3,nm3,at1,at2,at3,em1,em2,em3</t>
+        </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>70</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>ROE?????</t>
         </is>
@@ -1446,13 +1516,18 @@
           <t>{top_txt}</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>top_txt</t>
+        </is>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>71</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
@@ -1484,13 +1559,18 @@
           <t>{name}</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>80</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>????????</t>
         </is>
@@ -1522,13 +1602,18 @@
           <t>{name},{latest},{latest_val}</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>name,latest,latest_val</t>
+        </is>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>81</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>????????</t>
         </is>
@@ -1560,13 +1645,18 @@
           <t>{name},{latest},{latest_val}</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>name,latest,latest_val</t>
+        </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>82</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>????????</t>
         </is>
@@ -1598,13 +1688,18 @@
           <t>{name},{latest},{latest_val},{prev},{direction},{abs_diff},{abs_pct}</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>name,latest,latest_val,prev,direction,abs_diff,abs_pct</t>
+        </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>83</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>????????</t>
         </is>

--- a/config/key_ratio_rulebook.xlsx
+++ b/config/key_ratio_rulebook.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1705,6 +1705,428 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>roe_method_note</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>分解方法：采用Shapley分解（乘法体系），按三因子对ROE变动的边际贡献进行公平分摊。</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>???????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>roe_contrib_detail</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>三因子贡献：净利率{nm_contrib}个百分点（驱动占比{nm_share}），总资产周转率{at_contrib}个百分点（驱动占比{at_share}），权益乘数{em_contrib}个百分点（驱动占比{em_share}）。</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>roe_reconcile</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>分解校验：三因子贡献合计{contrib_sum}个百分点，对应ROE变动{roe_delta}个百分点。</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>?????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>trend_word_up</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wording</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ROE/????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>trend_word_down</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wording</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ROE/????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>trend_word_stable</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wording</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>基本稳定</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ROE/????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>roe_missing_years</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>杜邦分析所需年度不足，待补充。</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ROE??-???</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gm_missing_years</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>毛利率贡献分析所需年度不足，待补充。</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>?????-???</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gm_missing_segments</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>未识别到营业收入分项，毛利率贡献待补充。</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>?????-???</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>gm_negative_impact_summary</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>各分项按绝对影响占比展示，不采用简单占比</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>gm_segment_header</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>???????{y1}-{y3}??</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>y1,y3</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>?????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>gm_segment_line</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{name}???{ds}???????/??{dm}???????{di}???????{dt}??????????{net_share}???????{strength_share}?</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>name,ds,dm,di,dt,net_share,strength_share</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>gm_segment_summary</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>???????????{top_pos}???????{top_neg}?</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>top_pos,top_neg</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>?????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>gm_net_share_na</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>??????????0?</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>???????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>gm_top_fallback</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>???Top?????</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
